--- a/work_request_forms/018_preventive_maintenance_scheduling_form--work_request_forms.xlsx
+++ b/work_request_forms/018_preventive_maintenance_scheduling_form--work_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -717,7 +717,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Schedule Date</t>
+          <t>Schedule Date2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -740,7 +740,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Station Location</t>
+          <t>Station Location2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -763,7 +763,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vehicle Information</t>
+          <t>Vehicle Info2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Service Requirements</t>
+          <t>Service Requirements2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -809,7 +809,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Images with Signature</t>
+          <t>Images With Signature2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Service Type</t>
+          <t>Service Type2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Schedule Date</t>
+          <t>Schedule Date3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Schedule Time</t>
+          <t>Schedule Time2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -978,7 +978,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1114,12 +1114,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1164,29 +1164,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>images_with_signature_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1215,29 +1215,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>images_with_signature2_choices</t>
+          <t>service_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1249,46 +1249,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>service_type2_choices</t>
+          <t>images_with_signature2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>service_type2_choices</t>
+          <t>images_with_signature2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>service_type2_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>service_type2_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
